--- a/data/season2026/2026-2027 TPBL 例行賽球員數據表 - 新竹御嵿攻城獅.xlsx
+++ b/data/season2026/2026-2027 TPBL 例行賽球員數據表 - 新竹御嵿攻城獅.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE9E742-C94B-43F1-8F26-4A46188C109E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894540C5-DDC1-4A10-8B81-36C173992598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="平均數據" sheetId="1" r:id="rId1"/>
@@ -1003,7 +1003,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1097,12 +1097,8 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -1332,8 +1328,8 @@
     <col min="2" max="2" width="16.33203125" customWidth="1"/>
     <col min="3" max="3" width="9.109375" customWidth="1"/>
     <col min="4" max="4" width="5.44140625" customWidth="1"/>
-    <col min="5" max="5" width="8.5546875" customWidth="1"/>
-    <col min="6" max="6" width="4.77734375" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="4.77734375" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
     <col min="8" max="8" width="4.77734375" customWidth="1"/>
     <col min="9" max="10" width="8.5546875" customWidth="1"/>
@@ -1728,16 +1724,16 @@
       <c r="AG5" s="5">
         <v>1</v>
       </c>
-      <c r="AH5" s="49" t="s">
+      <c r="AH5" s="45" t="s">
         <v>254</v>
       </c>
-      <c r="AI5" s="50" t="s">
+      <c r="AI5" s="46" t="s">
         <v>255</v>
       </c>
       <c r="AK5" s="41" t="s">
         <v>206</v>
       </c>
-      <c r="AL5" s="42" t="s">
+      <c r="AL5" s="37" t="s">
         <v>41</v>
       </c>
       <c r="AM5" s="37">
@@ -1752,14 +1748,14 @@
       <c r="AP5" s="37">
         <v>-90.6</v>
       </c>
-      <c r="AQ5" s="45" t="s">
+      <c r="AQ5" s="38" t="s">
         <v>233</v>
       </c>
       <c r="AR5" s="16"/>
       <c r="AS5" s="41" t="s">
         <v>215</v>
       </c>
-      <c r="AT5" s="42" t="s">
+      <c r="AT5" s="37" t="s">
         <v>216</v>
       </c>
       <c r="AU5" s="37">
@@ -1778,7 +1774,7 @@
       <c r="AZ5" s="41" t="s">
         <v>242</v>
       </c>
-      <c r="BA5" s="42" t="s">
+      <c r="BA5" s="37" t="s">
         <v>222</v>
       </c>
       <c r="BB5" s="37">
@@ -1793,7 +1789,7 @@
       <c r="BE5" s="37">
         <v>2.7</v>
       </c>
-      <c r="BF5" s="45" t="s">
+      <c r="BF5" s="38" t="s">
         <v>243</v>
       </c>
     </row>
@@ -1897,16 +1893,16 @@
       <c r="AG6" s="5">
         <v>1</v>
       </c>
-      <c r="AH6" s="44" t="s">
+      <c r="AH6" s="39" t="s">
         <v>250</v>
       </c>
-      <c r="AI6" s="46" t="s">
+      <c r="AI6" s="40" t="s">
         <v>251</v>
       </c>
-      <c r="AK6" s="43" t="s">
+      <c r="AK6" s="42" t="s">
         <v>207</v>
       </c>
-      <c r="AL6" s="44" t="s">
+      <c r="AL6" s="39" t="s">
         <v>69</v>
       </c>
       <c r="AM6" s="39">
@@ -1921,14 +1917,14 @@
       <c r="AP6" s="39">
         <v>-20.100000000000001</v>
       </c>
-      <c r="AQ6" s="46" t="s">
+      <c r="AQ6" s="40" t="s">
         <v>234</v>
       </c>
       <c r="AR6" s="16"/>
-      <c r="AS6" s="43" t="s">
+      <c r="AS6" s="42" t="s">
         <v>217</v>
       </c>
-      <c r="AT6" s="44" t="s">
+      <c r="AT6" s="39" t="s">
         <v>218</v>
       </c>
       <c r="AU6" s="39">
@@ -1944,10 +1940,10 @@
         <v>7.7</v>
       </c>
       <c r="AY6" s="16"/>
-      <c r="AZ6" s="43" t="s">
+      <c r="AZ6" s="42" t="s">
         <v>244</v>
       </c>
-      <c r="BA6" s="44" t="s">
+      <c r="BA6" s="39" t="s">
         <v>245</v>
       </c>
       <c r="BB6" s="39">
@@ -1962,7 +1958,7 @@
       <c r="BE6" s="39">
         <v>-14.9</v>
       </c>
-      <c r="BF6" s="46" t="s">
+      <c r="BF6" s="40" t="s">
         <v>246</v>
       </c>
     </row>
@@ -2066,16 +2062,16 @@
       <c r="AG7" s="5">
         <v>8</v>
       </c>
-      <c r="AH7" s="47" t="s">
+      <c r="AH7" s="43" t="s">
         <v>252</v>
       </c>
-      <c r="AI7" s="48" t="s">
+      <c r="AI7" s="44" t="s">
         <v>253</v>
       </c>
       <c r="AK7" s="41" t="s">
         <v>208</v>
       </c>
-      <c r="AL7" s="42" t="s">
+      <c r="AL7" s="37" t="s">
         <v>94</v>
       </c>
       <c r="AM7" s="37">
@@ -2090,14 +2086,14 @@
       <c r="AP7" s="37">
         <v>-20.9</v>
       </c>
-      <c r="AQ7" s="45" t="s">
+      <c r="AQ7" s="38" t="s">
         <v>235</v>
       </c>
       <c r="AR7" s="16"/>
       <c r="AS7" s="41" t="s">
         <v>219</v>
       </c>
-      <c r="AT7" s="42" t="s">
+      <c r="AT7" s="37" t="s">
         <v>220</v>
       </c>
       <c r="AU7" s="37">
@@ -2116,7 +2112,7 @@
       <c r="AZ7" s="41" t="s">
         <v>247</v>
       </c>
-      <c r="BA7" s="42" t="s">
+      <c r="BA7" s="37" t="s">
         <v>248</v>
       </c>
       <c r="BB7" s="37">
@@ -2131,7 +2127,7 @@
       <c r="BE7" s="37">
         <v>1.5</v>
       </c>
-      <c r="BF7" s="45" t="s">
+      <c r="BF7" s="38" t="s">
         <v>249</v>
       </c>
     </row>
@@ -2235,16 +2231,16 @@
       <c r="AG8" s="5">
         <v>1</v>
       </c>
-      <c r="AH8" s="47" t="s">
+      <c r="AH8" s="43" t="s">
         <v>256</v>
       </c>
-      <c r="AI8" s="48" t="s">
+      <c r="AI8" s="44" t="s">
         <v>257</v>
       </c>
-      <c r="AK8" s="43" t="s">
+      <c r="AK8" s="42" t="s">
         <v>209</v>
       </c>
-      <c r="AL8" s="44" t="s">
+      <c r="AL8" s="39" t="s">
         <v>60</v>
       </c>
       <c r="AM8" s="39">
@@ -2259,7 +2255,7 @@
       <c r="AP8" s="39">
         <v>-23.9</v>
       </c>
-      <c r="AQ8" s="46" t="s">
+      <c r="AQ8" s="40" t="s">
         <v>236</v>
       </c>
       <c r="AR8" s="16"/>
@@ -2387,7 +2383,7 @@
       <c r="AK9" s="41" t="s">
         <v>210</v>
       </c>
-      <c r="AL9" s="42" t="s">
+      <c r="AL9" s="37" t="s">
         <v>52</v>
       </c>
       <c r="AM9" s="37">
@@ -2402,7 +2398,7 @@
       <c r="AP9" s="37">
         <v>-5.4</v>
       </c>
-      <c r="AQ9" s="45" t="s">
+      <c r="AQ9" s="38" t="s">
         <v>237</v>
       </c>
       <c r="AR9" s="16"/>
@@ -2527,10 +2523,10 @@
       <c r="AI10" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="AK10" s="43" t="s">
+      <c r="AK10" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="AL10" s="44" t="s">
+      <c r="AL10" s="39" t="s">
         <v>104</v>
       </c>
       <c r="AM10" s="39">
@@ -2545,7 +2541,7 @@
       <c r="AP10" s="39">
         <v>6.4</v>
       </c>
-      <c r="AQ10" s="46" t="s">
+      <c r="AQ10" s="40" t="s">
         <v>238</v>
       </c>
       <c r="AR10" s="16"/>
@@ -2673,7 +2669,7 @@
       <c r="AK11" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="AL11" s="42" t="s">
+      <c r="AL11" s="37" t="s">
         <v>114</v>
       </c>
       <c r="AM11" s="37">
@@ -2688,7 +2684,7 @@
       <c r="AP11" s="37">
         <v>3</v>
       </c>
-      <c r="AQ11" s="45" t="s">
+      <c r="AQ11" s="38" t="s">
         <v>239</v>
       </c>
       <c r="AR11" s="16"/>
@@ -2807,16 +2803,16 @@
       <c r="AG12" s="5">
         <v>3</v>
       </c>
-      <c r="AH12" s="49" t="s">
+      <c r="AH12" s="45" t="s">
         <v>258</v>
       </c>
-      <c r="AI12" s="50" t="s">
+      <c r="AI12" s="46" t="s">
         <v>259</v>
       </c>
-      <c r="AK12" s="43" t="s">
+      <c r="AK12" s="42" t="s">
         <v>213</v>
       </c>
-      <c r="AL12" s="44" t="s">
+      <c r="AL12" s="39" t="s">
         <v>89</v>
       </c>
       <c r="AM12" s="39">
@@ -2831,7 +2827,7 @@
       <c r="AP12" s="39">
         <v>10.3</v>
       </c>
-      <c r="AQ12" s="46" t="s">
+      <c r="AQ12" s="40" t="s">
         <v>240</v>
       </c>
       <c r="AR12" s="16"/>
@@ -2959,7 +2955,7 @@
       <c r="AK13" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="AL13" s="42" t="s">
+      <c r="AL13" s="37" t="s">
         <v>81</v>
       </c>
       <c r="AM13" s="37">
@@ -2974,7 +2970,7 @@
       <c r="AP13" s="37">
         <v>7.7</v>
       </c>
-      <c r="AQ13" s="45" t="s">
+      <c r="AQ13" s="38" t="s">
         <v>241</v>
       </c>
       <c r="AR13" s="16"/>
@@ -3222,10 +3218,10 @@
       <c r="AG15" s="5">
         <v>0</v>
       </c>
-      <c r="AH15" s="47" t="s">
+      <c r="AH15" s="43" t="s">
         <v>260</v>
       </c>
-      <c r="AI15" s="48" t="s">
+      <c r="AI15" s="44" t="s">
         <v>261</v>
       </c>
       <c r="AK15" s="17"/>
@@ -4830,8 +4826,9 @@
   <dimension ref="A1:BA1000"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="34" max="34" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="0" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="22.109375" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="19.88671875" hidden="1" customWidth="1"/>
     <col min="36" max="36" width="4.44140625" customWidth="1"/>
     <col min="37" max="37" width="37.44140625" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="9.5546875" bestFit="1" customWidth="1"/>
@@ -5189,7 +5186,7 @@
       <c r="AK5" s="41" t="s">
         <v>206</v>
       </c>
-      <c r="AL5" s="42" t="s">
+      <c r="AL5" s="37" t="s">
         <v>41</v>
       </c>
       <c r="AM5" s="37">
@@ -5208,10 +5205,10 @@
         <v>98.6</v>
       </c>
       <c r="AR5" s="30"/>
-      <c r="AS5" s="43" t="s">
+      <c r="AS5" s="42" t="s">
         <v>215</v>
       </c>
-      <c r="AT5" s="44" t="s">
+      <c r="AT5" s="39" t="s">
         <v>216</v>
       </c>
       <c r="AU5" s="39">
@@ -5337,10 +5334,10 @@
       <c r="AH6" s="25"/>
       <c r="AI6" s="25"/>
       <c r="AJ6" s="26"/>
-      <c r="AK6" s="43" t="s">
+      <c r="AK6" s="42" t="s">
         <v>207</v>
       </c>
-      <c r="AL6" s="44" t="s">
+      <c r="AL6" s="39" t="s">
         <v>69</v>
       </c>
       <c r="AM6" s="39">
@@ -5362,7 +5359,7 @@
       <c r="AS6" s="41" t="s">
         <v>217</v>
       </c>
-      <c r="AT6" s="42" t="s">
+      <c r="AT6" s="37" t="s">
         <v>218</v>
       </c>
       <c r="AU6" s="37">
@@ -5491,7 +5488,7 @@
       <c r="AK7" s="41" t="s">
         <v>208</v>
       </c>
-      <c r="AL7" s="42" t="s">
+      <c r="AL7" s="37" t="s">
         <v>94</v>
       </c>
       <c r="AM7" s="37">
@@ -5510,10 +5507,10 @@
         <v>29.8</v>
       </c>
       <c r="AR7" s="30"/>
-      <c r="AS7" s="43" t="s">
+      <c r="AS7" s="42" t="s">
         <v>219</v>
       </c>
-      <c r="AT7" s="44" t="s">
+      <c r="AT7" s="39" t="s">
         <v>220</v>
       </c>
       <c r="AU7" s="39">
@@ -5639,10 +5636,10 @@
       <c r="AH8" s="25"/>
       <c r="AI8" s="25"/>
       <c r="AJ8" s="26"/>
-      <c r="AK8" s="43" t="s">
+      <c r="AK8" s="42" t="s">
         <v>209</v>
       </c>
-      <c r="AL8" s="44" t="s">
+      <c r="AL8" s="39" t="s">
         <v>60</v>
       </c>
       <c r="AM8" s="39">
@@ -5779,7 +5776,7 @@
       <c r="AK9" s="41" t="s">
         <v>210</v>
       </c>
-      <c r="AL9" s="42" t="s">
+      <c r="AL9" s="37" t="s">
         <v>52</v>
       </c>
       <c r="AM9" s="37">
@@ -5798,10 +5795,10 @@
         <v>3.5</v>
       </c>
       <c r="AR9" s="30"/>
-      <c r="AS9" s="43" t="s">
+      <c r="AS9" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="AT9" s="44" t="s">
+      <c r="AT9" s="39" t="s">
         <v>222</v>
       </c>
       <c r="AU9" s="39">
@@ -5923,10 +5920,10 @@
       <c r="AH10" s="25"/>
       <c r="AI10" s="25"/>
       <c r="AJ10" s="26"/>
-      <c r="AK10" s="43" t="s">
+      <c r="AK10" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="AL10" s="44" t="s">
+      <c r="AL10" s="39" t="s">
         <v>104</v>
       </c>
       <c r="AM10" s="39">
@@ -5948,7 +5945,7 @@
       <c r="AS10" s="41" t="s">
         <v>223</v>
       </c>
-      <c r="AT10" s="42" t="s">
+      <c r="AT10" s="37" t="s">
         <v>224</v>
       </c>
       <c r="AU10" s="37">
@@ -6073,7 +6070,7 @@
       <c r="AK11" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="AL11" s="42" t="s">
+      <c r="AL11" s="37" t="s">
         <v>114</v>
       </c>
       <c r="AM11" s="37">
@@ -6092,10 +6089,10 @@
         <v>-25.1</v>
       </c>
       <c r="AR11" s="30"/>
-      <c r="AS11" s="43" t="s">
+      <c r="AS11" s="42" t="s">
         <v>225</v>
       </c>
-      <c r="AT11" s="44" t="s">
+      <c r="AT11" s="39" t="s">
         <v>226</v>
       </c>
       <c r="AU11" s="39">
@@ -6217,10 +6214,10 @@
       <c r="AH12" s="25"/>
       <c r="AI12" s="25"/>
       <c r="AJ12" s="26"/>
-      <c r="AK12" s="43" t="s">
+      <c r="AK12" s="42" t="s">
         <v>213</v>
       </c>
-      <c r="AL12" s="44" t="s">
+      <c r="AL12" s="39" t="s">
         <v>89</v>
       </c>
       <c r="AM12" s="39">
@@ -6355,7 +6352,7 @@
       <c r="AK13" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="AL13" s="42" t="s">
+      <c r="AL13" s="37" t="s">
         <v>81</v>
       </c>
       <c r="AM13" s="37">

--- a/data/season2026/2026-2027 TPBL 例行賽球員數據表 - 新竹御嵿攻城獅.xlsx
+++ b/data/season2026/2026-2027 TPBL 例行賽球員數據表 - 新竹御嵿攻城獅.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894540C5-DDC1-4A10-8B81-36C173992598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF10B57-F97C-48A4-9609-C24262CCC69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="平均數據" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="277">
   <si>
     <t>2026-2027 賽季 新竹御嵿攻城獅 (TPBL) 例行賽球員攻守數據表 - 平均數據 (待賽程展開)</t>
   </si>
@@ -788,34 +788,10 @@
     <t>奧獅頓低位單打搭配德魯高位掩護，具備陣容機動性。</t>
   </si>
   <si>
-    <t>禁區終結與籃下強攻(兩分佔比100%)</t>
-  </si>
-  <si>
-    <t>內線23投17中狂砍41分19籃板(9前場板)，禁區吃餅與二次進攻破壞力驚人。</t>
-  </si>
-  <si>
-    <t>高位策應與外線砲火(三分命中率80%)</t>
-  </si>
-  <si>
     <t>轟下23分12籃板8助攻5阻攻準大三元，三分球5投4中展現極高空間價值。</t>
   </si>
   <si>
-    <t>中長距離投射與快攻推進(多點分佈)</t>
-  </si>
-  <si>
-    <t>新秀首戰力拚近52分鐘攻下13分7籃板3抄截，正負值+9為全隊之冠。</t>
-  </si>
-  <si>
     <t>空間型四號位(兩分44% / 三分56%)</t>
-  </si>
-  <si>
-    <t>先發31分鐘投進2記三分貢獻10分3抄截，正負值+9，攻守兩端發揮穩定。</t>
-  </si>
-  <si>
-    <t>擋拆分球與組織串聯(傳導為主)</t>
-  </si>
-  <si>
-    <t>先發主控送出全隊最高9次助攻與6籃板，正負值+7，掌控球隊陣地戰節奏。</t>
   </si>
   <si>
     <t>禁區終結與衝搶(兩分佔比85%)</t>
@@ -824,7 +800,73 @@
     <t>替補出戰22分鐘攻下17分10籃板完成雙十，在二陣禁區提供即時火力支援。</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>中遠距離投射與快攻切入(兩分65%/三分35%)</t>
+  </si>
+  <si>
+    <t>首秀力戰近52分鐘攻下13分7籃板3抄截，正負值+9全隊第一，本土側翼基石。</t>
+  </si>
+  <si>
+    <t>禁區強攻與籃下二次進攻(兩分佔比100%)</t>
+  </si>
+  <si>
+    <t>內線23投17中狂暴砍下41分19籃板(9前場板)，禁區吃餅與籃板破壞力聯盟第一檔。</t>
+  </si>
+  <si>
+    <t>高位策應與空間外線砲火(三分命中率80%)</t>
+  </si>
+  <si>
+    <t>先發31分鐘投進2記三分貢獻10分3抄截，正負值+9，攻守兩端發揮穩定成熟。</t>
+  </si>
+  <si>
+    <t>禁區傳統巨塔(待例行賽出賽)</t>
+  </si>
+  <si>
+    <t>待例行賽賽程展開 / 先列入註冊名單與數據架構。</t>
+  </si>
+  <si>
+    <t>外線定點投射與快攻拋投(三分佔比56%)</t>
+  </si>
+  <si>
+    <t>替補出戰16分鐘貢獻11分3助攻，外線手感平穩，二陣主要持球攻擊點。</t>
+  </si>
+  <si>
+    <t>控球後衛組織推進(傳導為主)</t>
+  </si>
+  <si>
+    <t>首秀受困對手高壓防守手感欠佳得3分6板4助2抄截，持續調整職業半場節奏。</t>
+  </si>
+  <si>
+    <t>擋拆分球與節奏掌控(傳球優先)</t>
+  </si>
+  <si>
+    <t>先發主控送出全隊最高9次助攻與6籃板，正負值+7，掌控球隊陣地戰傳導節奏。</t>
+  </si>
+  <si>
+    <t>側翼外線射手(待例行賽出賽)</t>
+  </si>
+  <si>
+    <t>替補後場防守(積極拼搶)</t>
+  </si>
+  <si>
+    <t>替補出戰近5分鐘專注後場對位與防守壓迫，提供主力後衛喘息空間。</t>
+  </si>
+  <si>
+    <t>本土機動內線(待例行賽出賽)</t>
+  </si>
+  <si>
+    <t>外線冷箭與空手切入(eFG% 64.3%)</t>
+  </si>
+  <si>
+    <t>替補12分鐘高效率7投4中進帳9分2抄截，展現出色的側翼終結準星。</t>
+  </si>
+  <si>
+    <t>替補後衛組織(待例行賽出賽)</t>
+  </si>
+  <si>
+    <t>後衛防守替補(待例行賽出賽)</t>
+  </si>
+  <si>
+    <t>鋒線替補輪替(待例行賽出賽)</t>
   </si>
 </sst>
 </file>
@@ -1099,10 +1141,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1346,7 +1388,7 @@
     <col min="30" max="30" width="3.6640625" customWidth="1"/>
     <col min="31" max="32" width="7.21875" customWidth="1"/>
     <col min="33" max="33" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="42.21875" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="65.6640625" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="39.6640625" customWidth="1"/>
     <col min="38" max="38" width="12" customWidth="1"/>
@@ -1727,7 +1769,7 @@
       <c r="AH5" s="45" t="s">
         <v>254</v>
       </c>
-      <c r="AI5" s="46" t="s">
+      <c r="AI5" s="43" t="s">
         <v>255</v>
       </c>
       <c r="AK5" s="41" t="s">
@@ -1893,11 +1935,11 @@
       <c r="AG6" s="5">
         <v>1</v>
       </c>
-      <c r="AH6" s="39" t="s">
-        <v>250</v>
-      </c>
-      <c r="AI6" s="40" t="s">
-        <v>251</v>
+      <c r="AH6" s="46" t="s">
+        <v>256</v>
+      </c>
+      <c r="AI6" s="44" t="s">
+        <v>257</v>
       </c>
       <c r="AK6" s="42" t="s">
         <v>207</v>
@@ -2062,11 +2104,11 @@
       <c r="AG7" s="5">
         <v>8</v>
       </c>
-      <c r="AH7" s="43" t="s">
-        <v>252</v>
-      </c>
-      <c r="AI7" s="44" t="s">
-        <v>253</v>
+      <c r="AH7" s="45" t="s">
+        <v>258</v>
+      </c>
+      <c r="AI7" s="43" t="s">
+        <v>250</v>
       </c>
       <c r="AK7" s="41" t="s">
         <v>208</v>
@@ -2231,11 +2273,11 @@
       <c r="AG8" s="5">
         <v>1</v>
       </c>
-      <c r="AH8" s="43" t="s">
-        <v>256</v>
+      <c r="AH8" s="46" t="s">
+        <v>251</v>
       </c>
       <c r="AI8" s="44" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AK8" s="42" t="s">
         <v>209</v>
@@ -2374,11 +2416,11 @@
       <c r="AG9" s="5">
         <v>0</v>
       </c>
-      <c r="AH9" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="AI9" s="5" t="s">
-        <v>262</v>
+      <c r="AH9" s="45" t="s">
+        <v>260</v>
+      </c>
+      <c r="AI9" s="43" t="s">
+        <v>261</v>
       </c>
       <c r="AK9" s="41" t="s">
         <v>210</v>
@@ -2517,11 +2559,11 @@
       <c r="AG10" s="5">
         <v>3</v>
       </c>
-      <c r="AH10" s="5" t="s">
+      <c r="AH10" s="46" t="s">
         <v>262</v>
       </c>
-      <c r="AI10" s="5" t="s">
-        <v>262</v>
+      <c r="AI10" s="44" t="s">
+        <v>263</v>
       </c>
       <c r="AK10" s="42" t="s">
         <v>211</v>
@@ -2660,11 +2702,11 @@
       <c r="AG11" s="5">
         <v>1.33</v>
       </c>
-      <c r="AH11" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="AI11" s="5" t="s">
-        <v>262</v>
+      <c r="AH11" s="45" t="s">
+        <v>264</v>
+      </c>
+      <c r="AI11" s="43" t="s">
+        <v>265</v>
       </c>
       <c r="AK11" s="41" t="s">
         <v>212</v>
@@ -2803,11 +2845,11 @@
       <c r="AG12" s="5">
         <v>3</v>
       </c>
-      <c r="AH12" s="45" t="s">
-        <v>258</v>
-      </c>
-      <c r="AI12" s="46" t="s">
-        <v>259</v>
+      <c r="AH12" s="46" t="s">
+        <v>266</v>
+      </c>
+      <c r="AI12" s="44" t="s">
+        <v>267</v>
       </c>
       <c r="AK12" s="42" t="s">
         <v>213</v>
@@ -2946,11 +2988,11 @@
       <c r="AG13" s="5">
         <v>0</v>
       </c>
-      <c r="AH13" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="AI13" s="5" t="s">
-        <v>262</v>
+      <c r="AH13" s="45" t="s">
+        <v>268</v>
+      </c>
+      <c r="AI13" s="43" t="s">
+        <v>261</v>
       </c>
       <c r="AK13" s="41" t="s">
         <v>214</v>
@@ -3089,11 +3131,11 @@
       <c r="AG14" s="5">
         <v>0</v>
       </c>
-      <c r="AH14" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="AI14" s="5" t="s">
-        <v>262</v>
+      <c r="AH14" s="46" t="s">
+        <v>269</v>
+      </c>
+      <c r="AI14" s="44" t="s">
+        <v>270</v>
       </c>
       <c r="AK14" s="17"/>
       <c r="AL14" s="17"/>
@@ -3218,11 +3260,11 @@
       <c r="AG15" s="5">
         <v>0</v>
       </c>
-      <c r="AH15" s="43" t="s">
-        <v>260</v>
-      </c>
-      <c r="AI15" s="44" t="s">
-        <v>261</v>
+      <c r="AH15" s="45" t="s">
+        <v>252</v>
+      </c>
+      <c r="AI15" s="43" t="s">
+        <v>253</v>
       </c>
       <c r="AK15" s="17"/>
       <c r="AL15" s="17"/>
@@ -3347,11 +3389,11 @@
       <c r="AG16" s="5">
         <v>0</v>
       </c>
-      <c r="AH16" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="AI16" s="5" t="s">
-        <v>262</v>
+      <c r="AH16" s="46" t="s">
+        <v>271</v>
+      </c>
+      <c r="AI16" s="44" t="s">
+        <v>261</v>
       </c>
       <c r="AK16" s="17"/>
       <c r="AL16" s="17"/>
@@ -3476,11 +3518,11 @@
       <c r="AG17" s="5">
         <v>0</v>
       </c>
-      <c r="AH17" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="AI17" s="5" t="s">
-        <v>262</v>
+      <c r="AH17" s="45" t="s">
+        <v>272</v>
+      </c>
+      <c r="AI17" s="43" t="s">
+        <v>273</v>
       </c>
       <c r="AK17" s="17"/>
       <c r="AL17" s="17"/>
@@ -3605,11 +3647,11 @@
       <c r="AG18" s="5">
         <v>0</v>
       </c>
-      <c r="AH18" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="AI18" s="5" t="s">
-        <v>262</v>
+      <c r="AH18" s="46" t="s">
+        <v>274</v>
+      </c>
+      <c r="AI18" s="44" t="s">
+        <v>261</v>
       </c>
       <c r="AK18" s="17"/>
       <c r="AL18" s="17"/>
@@ -3734,11 +3776,11 @@
       <c r="AG19" s="5">
         <v>0</v>
       </c>
-      <c r="AH19" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="AI19" s="5" t="s">
-        <v>262</v>
+      <c r="AH19" s="45" t="s">
+        <v>275</v>
+      </c>
+      <c r="AI19" s="43" t="s">
+        <v>261</v>
       </c>
       <c r="AK19" s="17"/>
       <c r="AL19" s="17"/>
@@ -3863,11 +3905,11 @@
       <c r="AG20" s="5">
         <v>0</v>
       </c>
-      <c r="AH20" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="AI20" s="5" t="s">
-        <v>262</v>
+      <c r="AH20" s="46" t="s">
+        <v>276</v>
+      </c>
+      <c r="AI20" s="44" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/data/season2026/2026-2027 TPBL 例行賽球員數據表 - 新竹御嵿攻城獅.xlsx
+++ b/data/season2026/2026-2027 TPBL 例行賽球員數據表 - 新竹御嵿攻城獅.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF10B57-F97C-48A4-9609-C24262CCC69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9CEF89B-3850-4827-B964-CB1500CEF774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="平均數據" sheetId="1" r:id="rId1"/>
@@ -620,9 +620,6 @@
     <t>【單場最佳陣容與搭檔效益】</t>
   </si>
   <si>
-    <t>【單場焦點對位交鋒 (WOWY: 呂威霆 vs 夢想家高柏鎧)】</t>
-  </si>
-  <si>
     <t>在場時間</t>
   </si>
   <si>
@@ -867,6 +864,9 @@
   </si>
   <si>
     <t>鋒線替補輪替(待例行賽出賽)</t>
+  </si>
+  <si>
+    <t>【單場焦點對位交鋒】</t>
   </si>
 </sst>
 </file>
@@ -1767,13 +1767,13 @@
         <v>1</v>
       </c>
       <c r="AH5" s="45" t="s">
+        <v>253</v>
+      </c>
+      <c r="AI5" s="43" t="s">
         <v>254</v>
       </c>
-      <c r="AI5" s="43" t="s">
-        <v>255</v>
-      </c>
       <c r="AK5" s="41" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AL5" s="37" t="s">
         <v>41</v>
@@ -1791,14 +1791,14 @@
         <v>-90.6</v>
       </c>
       <c r="AQ5" s="38" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AR5" s="16"/>
       <c r="AS5" s="41" t="s">
+        <v>214</v>
+      </c>
+      <c r="AT5" s="37" t="s">
         <v>215</v>
-      </c>
-      <c r="AT5" s="37" t="s">
-        <v>216</v>
       </c>
       <c r="AU5" s="37">
         <v>9</v>
@@ -1814,10 +1814,10 @@
       </c>
       <c r="AY5" s="16"/>
       <c r="AZ5" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BA5" s="37" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="BB5" s="37">
         <v>3</v>
@@ -1832,7 +1832,7 @@
         <v>2.7</v>
       </c>
       <c r="BF5" s="38" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="1:58" ht="13.2" x14ac:dyDescent="0.25">
@@ -1936,13 +1936,13 @@
         <v>1</v>
       </c>
       <c r="AH6" s="46" t="s">
+        <v>255</v>
+      </c>
+      <c r="AI6" s="44" t="s">
         <v>256</v>
       </c>
-      <c r="AI6" s="44" t="s">
-        <v>257</v>
-      </c>
       <c r="AK6" s="42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL6" s="39" t="s">
         <v>69</v>
@@ -1960,14 +1960,14 @@
         <v>-20.100000000000001</v>
       </c>
       <c r="AQ6" s="40" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AR6" s="16"/>
       <c r="AS6" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="AT6" s="39" t="s">
         <v>217</v>
-      </c>
-      <c r="AT6" s="39" t="s">
-        <v>218</v>
       </c>
       <c r="AU6" s="39">
         <v>4</v>
@@ -1983,10 +1983,10 @@
       </c>
       <c r="AY6" s="16"/>
       <c r="AZ6" s="42" t="s">
+        <v>243</v>
+      </c>
+      <c r="BA6" s="39" t="s">
         <v>244</v>
-      </c>
-      <c r="BA6" s="39" t="s">
-        <v>245</v>
       </c>
       <c r="BB6" s="39">
         <v>-5</v>
@@ -2001,7 +2001,7 @@
         <v>-14.9</v>
       </c>
       <c r="BF6" s="40" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="1:58" ht="13.2" x14ac:dyDescent="0.25">
@@ -2105,13 +2105,13 @@
         <v>8</v>
       </c>
       <c r="AH7" s="45" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AI7" s="43" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AK7" s="41" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AL7" s="37" t="s">
         <v>94</v>
@@ -2129,14 +2129,14 @@
         <v>-20.9</v>
       </c>
       <c r="AQ7" s="38" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AR7" s="16"/>
       <c r="AS7" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="AT7" s="37" t="s">
         <v>219</v>
-      </c>
-      <c r="AT7" s="37" t="s">
-        <v>220</v>
       </c>
       <c r="AU7" s="37">
         <v>-5</v>
@@ -2152,10 +2152,10 @@
       </c>
       <c r="AY7" s="16"/>
       <c r="AZ7" s="41" t="s">
+        <v>246</v>
+      </c>
+      <c r="BA7" s="37" t="s">
         <v>247</v>
-      </c>
-      <c r="BA7" s="37" t="s">
-        <v>248</v>
       </c>
       <c r="BB7" s="37">
         <v>1</v>
@@ -2170,7 +2170,7 @@
         <v>1.5</v>
       </c>
       <c r="BF7" s="38" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" spans="1:58" ht="13.2" x14ac:dyDescent="0.25">
@@ -2274,13 +2274,13 @@
         <v>1</v>
       </c>
       <c r="AH8" s="46" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AI8" s="44" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AK8" s="42" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AL8" s="39" t="s">
         <v>60</v>
@@ -2298,7 +2298,7 @@
         <v>-23.9</v>
       </c>
       <c r="AQ8" s="40" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AR8" s="16"/>
       <c r="AS8" s="17"/>
@@ -2417,13 +2417,13 @@
         <v>0</v>
       </c>
       <c r="AH9" s="45" t="s">
+        <v>259</v>
+      </c>
+      <c r="AI9" s="43" t="s">
         <v>260</v>
       </c>
-      <c r="AI9" s="43" t="s">
-        <v>261</v>
-      </c>
       <c r="AK9" s="41" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AL9" s="37" t="s">
         <v>52</v>
@@ -2441,7 +2441,7 @@
         <v>-5.4</v>
       </c>
       <c r="AQ9" s="38" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AR9" s="16"/>
       <c r="AS9" s="17"/>
@@ -2560,13 +2560,13 @@
         <v>3</v>
       </c>
       <c r="AH10" s="46" t="s">
+        <v>261</v>
+      </c>
+      <c r="AI10" s="44" t="s">
         <v>262</v>
       </c>
-      <c r="AI10" s="44" t="s">
-        <v>263</v>
-      </c>
       <c r="AK10" s="42" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AL10" s="39" t="s">
         <v>104</v>
@@ -2584,7 +2584,7 @@
         <v>6.4</v>
       </c>
       <c r="AQ10" s="40" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AR10" s="16"/>
       <c r="AS10" s="17"/>
@@ -2703,13 +2703,13 @@
         <v>1.33</v>
       </c>
       <c r="AH11" s="45" t="s">
+        <v>263</v>
+      </c>
+      <c r="AI11" s="43" t="s">
         <v>264</v>
       </c>
-      <c r="AI11" s="43" t="s">
-        <v>265</v>
-      </c>
       <c r="AK11" s="41" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AL11" s="37" t="s">
         <v>114</v>
@@ -2727,7 +2727,7 @@
         <v>3</v>
       </c>
       <c r="AQ11" s="38" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AR11" s="16"/>
       <c r="AS11" s="17"/>
@@ -2846,13 +2846,13 @@
         <v>3</v>
       </c>
       <c r="AH12" s="46" t="s">
+        <v>265</v>
+      </c>
+      <c r="AI12" s="44" t="s">
         <v>266</v>
       </c>
-      <c r="AI12" s="44" t="s">
-        <v>267</v>
-      </c>
       <c r="AK12" s="42" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AL12" s="39" t="s">
         <v>89</v>
@@ -2870,7 +2870,7 @@
         <v>10.3</v>
       </c>
       <c r="AQ12" s="40" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AR12" s="16"/>
       <c r="AS12" s="17"/>
@@ -2989,13 +2989,13 @@
         <v>0</v>
       </c>
       <c r="AH13" s="45" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AI13" s="43" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AK13" s="41" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AL13" s="37" t="s">
         <v>81</v>
@@ -3013,7 +3013,7 @@
         <v>7.7</v>
       </c>
       <c r="AQ13" s="38" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AR13" s="16"/>
       <c r="AS13" s="17"/>
@@ -3132,10 +3132,10 @@
         <v>0</v>
       </c>
       <c r="AH14" s="46" t="s">
+        <v>268</v>
+      </c>
+      <c r="AI14" s="44" t="s">
         <v>269</v>
-      </c>
-      <c r="AI14" s="44" t="s">
-        <v>270</v>
       </c>
       <c r="AK14" s="17"/>
       <c r="AL14" s="17"/>
@@ -3261,10 +3261,10 @@
         <v>0</v>
       </c>
       <c r="AH15" s="45" t="s">
+        <v>251</v>
+      </c>
+      <c r="AI15" s="43" t="s">
         <v>252</v>
-      </c>
-      <c r="AI15" s="43" t="s">
-        <v>253</v>
       </c>
       <c r="AK15" s="17"/>
       <c r="AL15" s="17"/>
@@ -3390,10 +3390,10 @@
         <v>0</v>
       </c>
       <c r="AH16" s="46" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AI16" s="44" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AK16" s="17"/>
       <c r="AL16" s="17"/>
@@ -3519,10 +3519,10 @@
         <v>0</v>
       </c>
       <c r="AH17" s="45" t="s">
+        <v>271</v>
+      </c>
+      <c r="AI17" s="43" t="s">
         <v>272</v>
-      </c>
-      <c r="AI17" s="43" t="s">
-        <v>273</v>
       </c>
       <c r="AK17" s="17"/>
       <c r="AL17" s="17"/>
@@ -3648,10 +3648,10 @@
         <v>0</v>
       </c>
       <c r="AH18" s="46" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AI18" s="44" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AK18" s="17"/>
       <c r="AL18" s="17"/>
@@ -3777,10 +3777,10 @@
         <v>0</v>
       </c>
       <c r="AH19" s="45" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AI19" s="43" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AK19" s="17"/>
       <c r="AL19" s="17"/>
@@ -3906,10 +3906,10 @@
         <v>0</v>
       </c>
       <c r="AH20" s="46" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AI20" s="44" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -4868,7 +4868,7 @@
   <dimension ref="A1:BA1000"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="6" width="0" hidden="1" customWidth="1"/>
+    <col min="5" max="6" width="8.88671875" customWidth="1"/>
     <col min="34" max="34" width="22.109375" hidden="1" customWidth="1"/>
     <col min="35" max="35" width="19.88671875" hidden="1" customWidth="1"/>
     <col min="36" max="36" width="4.44140625" customWidth="1"/>
@@ -4963,7 +4963,7 @@
       <c r="AX3" s="23"/>
       <c r="AY3" s="21"/>
       <c r="AZ3" s="22" t="s">
-        <v>194</v>
+        <v>276</v>
       </c>
       <c r="BA3" s="23"/>
     </row>
@@ -5078,32 +5078,32 @@
         <v>3</v>
       </c>
       <c r="AL4" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="AM4" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="AM4" s="23" t="s">
+      <c r="AN4" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="AN4" s="23" t="s">
+      <c r="AO4" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="AO4" s="23" t="s">
+      <c r="AP4" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="AP4" s="23" t="s">
+      <c r="AQ4" s="23" t="s">
         <v>199</v>
-      </c>
-      <c r="AQ4" s="23" t="s">
-        <v>200</v>
       </c>
       <c r="AR4" s="24"/>
       <c r="AS4" s="22" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AT4" s="23" t="s">
         <v>146</v>
       </c>
       <c r="AU4" s="23" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AV4" s="23" t="s">
         <v>185</v>
@@ -5116,10 +5116,10 @@
       </c>
       <c r="AY4" s="24"/>
       <c r="AZ4" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="BA4" s="23" t="s">
         <v>203</v>
-      </c>
-      <c r="BA4" s="23" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:53" x14ac:dyDescent="0.25">
@@ -5226,7 +5226,7 @@
       <c r="AI5" s="25"/>
       <c r="AJ5" s="26"/>
       <c r="AK5" s="41" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AL5" s="37" t="s">
         <v>41</v>
@@ -5248,10 +5248,10 @@
       </c>
       <c r="AR5" s="30"/>
       <c r="AS5" s="42" t="s">
+        <v>214</v>
+      </c>
+      <c r="AT5" s="39" t="s">
         <v>215</v>
-      </c>
-      <c r="AT5" s="39" t="s">
-        <v>216</v>
       </c>
       <c r="AU5" s="39">
         <v>9</v>
@@ -5267,10 +5267,10 @@
       </c>
       <c r="AY5" s="30"/>
       <c r="AZ5" t="s">
+        <v>226</v>
+      </c>
+      <c r="BA5" t="s">
         <v>227</v>
-      </c>
-      <c r="BA5" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:53" x14ac:dyDescent="0.25">
@@ -5377,7 +5377,7 @@
       <c r="AI6" s="25"/>
       <c r="AJ6" s="26"/>
       <c r="AK6" s="42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL6" s="39" t="s">
         <v>69</v>
@@ -5399,10 +5399,10 @@
       </c>
       <c r="AR6" s="30"/>
       <c r="AS6" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="AT6" s="37" t="s">
         <v>217</v>
-      </c>
-      <c r="AT6" s="37" t="s">
-        <v>218</v>
       </c>
       <c r="AU6" s="37">
         <v>4</v>
@@ -5418,10 +5418,10 @@
       </c>
       <c r="AY6" s="30"/>
       <c r="AZ6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="BA6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" spans="1:53" x14ac:dyDescent="0.25">
@@ -5528,7 +5528,7 @@
       <c r="AI7" s="25"/>
       <c r="AJ7" s="26"/>
       <c r="AK7" s="41" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AL7" s="37" t="s">
         <v>94</v>
@@ -5550,10 +5550,10 @@
       </c>
       <c r="AR7" s="30"/>
       <c r="AS7" s="42" t="s">
+        <v>218</v>
+      </c>
+      <c r="AT7" s="39" t="s">
         <v>219</v>
-      </c>
-      <c r="AT7" s="39" t="s">
-        <v>220</v>
       </c>
       <c r="AU7" s="39">
         <v>-5</v>
@@ -5569,10 +5569,10 @@
       </c>
       <c r="AY7" s="30"/>
       <c r="AZ7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BA7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:53" x14ac:dyDescent="0.25">
@@ -5679,7 +5679,7 @@
       <c r="AI8" s="25"/>
       <c r="AJ8" s="26"/>
       <c r="AK8" s="42" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AL8" s="39" t="s">
         <v>60</v>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="AR8" s="30"/>
       <c r="AS8" s="32" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AT8" s="33"/>
       <c r="AU8" s="34"/>
@@ -5816,7 +5816,7 @@
       <c r="AI9" s="25"/>
       <c r="AJ9" s="26"/>
       <c r="AK9" s="41" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AL9" s="37" t="s">
         <v>52</v>
@@ -5838,10 +5838,10 @@
       </c>
       <c r="AR9" s="30"/>
       <c r="AS9" s="42" t="s">
+        <v>220</v>
+      </c>
+      <c r="AT9" s="39" t="s">
         <v>221</v>
-      </c>
-      <c r="AT9" s="39" t="s">
-        <v>222</v>
       </c>
       <c r="AU9" s="39">
         <v>3</v>
@@ -5963,7 +5963,7 @@
       <c r="AI10" s="25"/>
       <c r="AJ10" s="26"/>
       <c r="AK10" s="42" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AL10" s="39" t="s">
         <v>104</v>
@@ -5985,10 +5985,10 @@
       </c>
       <c r="AR10" s="30"/>
       <c r="AS10" s="41" t="s">
+        <v>222</v>
+      </c>
+      <c r="AT10" s="37" t="s">
         <v>223</v>
-      </c>
-      <c r="AT10" s="37" t="s">
-        <v>224</v>
       </c>
       <c r="AU10" s="37">
         <v>8</v>
@@ -6110,7 +6110,7 @@
       <c r="AI11" s="25"/>
       <c r="AJ11" s="26"/>
       <c r="AK11" s="41" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AL11" s="37" t="s">
         <v>114</v>
@@ -6132,10 +6132,10 @@
       </c>
       <c r="AR11" s="30"/>
       <c r="AS11" s="42" t="s">
+        <v>224</v>
+      </c>
+      <c r="AT11" s="39" t="s">
         <v>225</v>
-      </c>
-      <c r="AT11" s="39" t="s">
-        <v>226</v>
       </c>
       <c r="AU11" s="39">
         <v>9</v>
@@ -6257,7 +6257,7 @@
       <c r="AI12" s="25"/>
       <c r="AJ12" s="26"/>
       <c r="AK12" s="42" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AL12" s="39" t="s">
         <v>89</v>
@@ -6392,7 +6392,7 @@
       <c r="AI13" s="25"/>
       <c r="AJ13" s="26"/>
       <c r="AK13" s="41" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AL13" s="37" t="s">
         <v>81</v>
